--- a/output/yearly_surface_area_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_37_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641263794</v>
+        <v>10.84497650955917</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890722221412</v>
+        <v>37.789072559861</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.592435834017332</v>
+        <v>6.060328578315561</v>
       </c>
       <c r="C2" t="n">
-        <v>12.8648219164502</v>
+        <v>7.268860002243384</v>
       </c>
       <c r="D2" t="n">
-        <v>28.95370329364693</v>
+        <v>26.29316701513807</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.89096925156637</v>
+        <v>19.22752878767378</v>
       </c>
       <c r="C3" t="n">
-        <v>39.94731408580272</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D3" t="n">
-        <v>68.38363633931158</v>
+        <v>74.09740797802802</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.1492920709703</v>
+        <v>39.46233071990478</v>
       </c>
       <c r="C4" t="n">
-        <v>94.99292611521713</v>
+        <v>66.40443296755001</v>
       </c>
       <c r="D4" t="n">
-        <v>68.28055283036566</v>
+        <v>94.48241730900878</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.59526757060561</v>
+        <v>43.58959806855839</v>
       </c>
       <c r="C5" t="n">
-        <v>128.4862307933013</v>
+        <v>107.6240920780566</v>
       </c>
       <c r="D5" t="n">
-        <v>49.16101629015904</v>
+        <v>69.94952392758525</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>35.54221213684728</v>
       </c>
       <c r="C6" t="n">
-        <v>132.0254312671111</v>
+        <v>121.2379874928471</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>46.69192081397831</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>128.3370051422558</v>
+        <v>110.6704552043344</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>91.54306468249383</v>
+        <v>72.60024272905163</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>50.69843319500952</v>
+        <v>38.60624672180155</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.68756678388216</v>
+        <v>7.691090784944786</v>
       </c>
       <c r="C21" t="n">
-        <v>94.17269310255645</v>
+        <v>94.21586211557363</v>
       </c>
       <c r="D21" t="n">
-        <v>8.64851263186743</v>
+        <v>8.652477133062884</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.587126184868598</v>
+        <v>5.876741757621406</v>
       </c>
       <c r="C2" t="n">
-        <v>10.25533651856218</v>
+        <v>11.95376004690916</v>
       </c>
       <c r="D2" t="n">
-        <v>25.18281036163494</v>
+        <v>24.14510303824605</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.30115986549229</v>
+        <v>19.67913273162732</v>
       </c>
       <c r="C3" t="n">
-        <v>44.77260405217579</v>
+        <v>28.83393007372882</v>
       </c>
       <c r="D3" t="n">
-        <v>74.17594779436776</v>
+        <v>76.91993262773759</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.04719030972863</v>
+        <v>38.05843150283185</v>
       </c>
       <c r="C4" t="n">
-        <v>97.18811398191299</v>
+        <v>70.32258805519903</v>
       </c>
       <c r="D4" t="n">
-        <v>84.06803766235862</v>
+        <v>107.6280190688736</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.78594760940775</v>
+        <v>50.41274461307373</v>
       </c>
       <c r="C5" t="n">
-        <v>149.0293015046659</v>
+        <v>113.588209381356</v>
       </c>
       <c r="D5" t="n">
-        <v>59.78843518863076</v>
+        <v>84.30758410219485</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.51833139677587</v>
+        <v>46.08814597586652</v>
       </c>
       <c r="C6" t="n">
-        <v>165.4745572985042</v>
+        <v>144.9462128027034</v>
       </c>
       <c r="D6" t="n">
-        <v>44.63908636439822</v>
+        <v>56.51332484726341</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.29695513723482</v>
+        <v>32.93763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>156.3639386030937</v>
+        <v>140.2544405241078</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.61041039233004</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>127.3424947178538</v>
+        <v>107.7320843255237</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>79.87499321752047</v>
+        <v>62.01405723415825</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.863516699807469</v>
+        <v>7.871474008735873</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2257170974971</v>
+        <v>102.3291621135664</v>
       </c>
       <c r="D21" t="n">
-        <v>9.829395874759337</v>
+        <v>9.839342510919842</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.670574739729576</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C2" t="n">
-        <v>11.99302995507903</v>
+        <v>9.959830459583891</v>
       </c>
       <c r="D2" t="n">
-        <v>29.66743387463436</v>
+        <v>28.79171492244621</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.62866268808323</v>
+        <v>19.32570355809846</v>
       </c>
       <c r="C3" t="n">
-        <v>42.11697651218817</v>
+        <v>36.93825737228624</v>
       </c>
       <c r="D3" t="n">
-        <v>75.63384313517427</v>
+        <v>78.21583959734339</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.28517416478385</v>
+        <v>36.98636300979434</v>
       </c>
       <c r="C4" t="n">
-        <v>102.3442529246172</v>
+        <v>70.90967318233861</v>
       </c>
       <c r="D4" t="n">
-        <v>96.35853717182444</v>
+        <v>116.6129740581404</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.60218086226435</v>
+        <v>52.86711387369075</v>
       </c>
       <c r="C5" t="n">
-        <v>160.1230505626548</v>
+        <v>119.2578023733813</v>
       </c>
       <c r="D5" t="n">
-        <v>72.62478642165782</v>
+        <v>98.59201319898595</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.11331156327844</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="C6" t="n">
-        <v>195.8243058275901</v>
+        <v>160.684610249484</v>
       </c>
       <c r="D6" t="n">
-        <v>50.79758971313847</v>
+        <v>67.50202690089796</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.08221443191203</v>
+        <v>41.9206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9603267901238</v>
+        <v>169.0598999144135</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>47.49008169753095</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.20284622634736</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C8" t="n">
-        <v>160.6384681073843</v>
+        <v>140.9446091601933</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1503,7 +1503,7 @@
         <v>13.7562488319063</v>
       </c>
       <c r="C9" t="n">
-        <v>113.0453029009074</v>
+        <v>92.96561710594743</v>
       </c>
       <c r="D9" t="n">
         <v>36.72030938194344</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>64.48609795345175</v>
+        <v>52.3860574986098</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>40.51476425885736</v>
+        <v>37.13853390395258</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.022208289352772</v>
+        <v>8.036138863555019</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3025879424315</v>
+        <v>110.4969093738815</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03053639786006</v>
+        <v>11.04969093738815</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.399612373357456</v>
+        <v>6.757369448330795</v>
       </c>
       <c r="C2" t="n">
-        <v>8.346818981506383</v>
+        <v>6.772095663894499</v>
       </c>
       <c r="D2" t="n">
-        <v>24.45926230360503</v>
+        <v>23.63361248433347</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.49183990429443</v>
+        <v>24.30316441862979</v>
       </c>
       <c r="C3" t="n">
-        <v>63.29327449279187</v>
+        <v>52.69039928692631</v>
       </c>
       <c r="D3" t="n">
-        <v>80.36095833112267</v>
+        <v>85.85874547490481</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.90082778633785</v>
+        <v>25.39781310886498</v>
       </c>
       <c r="C4" t="n">
-        <v>134.953002921175</v>
+        <v>98.32399607572655</v>
       </c>
       <c r="D4" t="n">
-        <v>88.99444764226911</v>
+        <v>111.5589368766778</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.2252464970958</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="C5" t="n">
-        <v>116.9997826536137</v>
+        <v>96.01492547533807</v>
       </c>
       <c r="D5" t="n">
-        <v>49.87278337573798</v>
+        <v>66.83247496660162</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.47929816831747</v>
+        <v>26.00256969468102</v>
       </c>
       <c r="C6" t="n">
-        <v>125.1021464567626</v>
+        <v>111.3360801478138</v>
       </c>
       <c r="D6" t="n">
-        <v>28.17615911188346</v>
+        <v>31.27553661419064</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>112.9461463827785</v>
+        <v>99.11233948223673</v>
       </c>
       <c r="D7" t="n">
-        <v>27.72750041104266</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1800,7 +1800,7 @@
         <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>83.28165775125692</v>
+        <v>68.51126354086365</v>
       </c>
       <c r="D8" t="n">
         <v>27.03733177495716</v>
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>49.14530832689106</v>
+        <v>39.93749660876023</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
         <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.480295611554943</v>
+        <v>4.070325981807276</v>
       </c>
       <c r="C2" t="n">
-        <v>4.208752408106076</v>
+        <v>3.218168974521045</v>
       </c>
       <c r="D2" t="n">
-        <v>17.24636192050372</v>
+        <v>16.21847207415731</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.25974653546468</v>
+        <v>24.47497026687298</v>
       </c>
       <c r="C3" t="n">
-        <v>48.89594441001239</v>
+        <v>40.11421119552467</v>
       </c>
       <c r="D3" t="n">
-        <v>82.20664401510668</v>
+        <v>85.30405802200535</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.61776565234527</v>
+        <v>34.52315801983909</v>
       </c>
       <c r="C4" t="n">
-        <v>149.3876394167159</v>
+        <v>116.9192793418654</v>
       </c>
       <c r="D4" t="n">
-        <v>104.411813589761</v>
+        <v>127.4612861900676</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.53864499892879</v>
+        <v>35.56381058634071</v>
       </c>
       <c r="C5" t="n">
-        <v>177.6472470834604</v>
+        <v>137.0274358202486</v>
       </c>
       <c r="D5" t="n">
-        <v>64.91806694332035</v>
+        <v>84.50393364304422</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.94723197034471</v>
+        <v>31.35603992593888</v>
       </c>
       <c r="C6" t="n">
-        <v>155.1701333947296</v>
+        <v>132.9512193522158</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2881194078966</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -2097,10 +2097,10 @@
         <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>140.3742137440259</v>
+        <v>126.0613139638117</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94330497952771</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>107.8989814352457</v>
+        <v>90.12443924985719</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.860231973098458</v>
+        <v>3.98000519301657</v>
       </c>
       <c r="C2" t="n">
-        <v>9.007535186464485</v>
+        <v>4.565126824747668</v>
       </c>
       <c r="D2" t="n">
-        <v>19.11168255857266</v>
+        <v>21.01136436629024</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57190124768616</v>
+        <v>19.30115986549229</v>
       </c>
       <c r="C3" t="n">
-        <v>31.8871654339364</v>
+        <v>25.55980148006571</v>
       </c>
       <c r="D3" t="n">
-        <v>77.22918315457534</v>
+        <v>78.9963290222196</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.00814138573701</v>
+        <v>40.16428032844126</v>
       </c>
       <c r="C4" t="n">
-        <v>137.0205635863188</v>
+        <v>108.3044432370996</v>
       </c>
       <c r="D4" t="n">
-        <v>119.0761790480956</v>
+        <v>138.9732597700657</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.99363615435157</v>
+        <v>43.07418052382881</v>
       </c>
       <c r="C5" t="n">
-        <v>223.3966901013617</v>
+        <v>175.4628584415112</v>
       </c>
       <c r="D5" t="n">
-        <v>83.79216655746528</v>
+        <v>106.5932569885975</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>39.08435785376978</v>
       </c>
       <c r="C6" t="n">
-        <v>212.5287430153495</v>
+        <v>174.3299215908104</v>
       </c>
       <c r="D6" t="n">
-        <v>43.35103337642641</v>
+        <v>53.09193409796327</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.59532432386784</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>179.7796030970844</v>
+        <v>158.1605369018654</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>143.2811686963007</v>
+        <v>125.2562808463293</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>86.30936767115406</v>
+        <v>73.44061876388687</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>41.56719779780995</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.337541283811655</v>
+        <v>2.372884201164541</v>
       </c>
       <c r="C2" t="n">
-        <v>4.379576508645021</v>
+        <v>2.1392282475538</v>
       </c>
       <c r="D2" t="n">
-        <v>13.36747674102457</v>
+        <v>14.67810992619406</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.5915362017711</v>
+        <v>18.92318699935727</v>
       </c>
       <c r="C3" t="n">
-        <v>35.22510762837555</v>
+        <v>23.86137795171873</v>
       </c>
       <c r="D3" t="n">
-        <v>77.40098900281853</v>
+        <v>79.9338980797753</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.23710958500477</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="C4" t="n">
-        <v>130.6902543893354</v>
+        <v>102.7781854098943</v>
       </c>
       <c r="D4" t="n">
-        <v>128.6482191645021</v>
+        <v>147.677434915918</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.07355862902306</v>
+        <v>44.1541029985003</v>
       </c>
       <c r="C5" t="n">
-        <v>265.3418607653067</v>
+        <v>210.2412708644545</v>
       </c>
       <c r="D5" t="n">
-        <v>89.06906046779189</v>
+        <v>112.4837432140783</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.53842401475054</v>
+        <v>31.03402667894593</v>
       </c>
       <c r="C6" t="n">
-        <v>247.9904518404486</v>
+        <v>207.7387959663294</v>
       </c>
       <c r="D6" t="n">
-        <v>43.1095234411817</v>
+        <v>52.00513938936205</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.60559946480004</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="C7" t="n">
-        <v>186.7863364622939</v>
+        <v>166.1254560264198</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>105.7293190088602</v>
+        <v>92.12720456652069</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>34.94530953266521</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.211296740591317</v>
+        <v>2.606540154775282</v>
       </c>
       <c r="C2" t="n">
-        <v>7.590873249236338</v>
+        <v>4.487568756112171</v>
       </c>
       <c r="D2" t="n">
-        <v>15.32115467247572</v>
+        <v>16.29210315197582</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.40929098167968</v>
+        <v>13.72483290537041</v>
       </c>
       <c r="C3" t="n">
-        <v>26.33047342789946</v>
+        <v>15.9583089325319</v>
       </c>
       <c r="D3" t="n">
-        <v>70.97054154000192</v>
+        <v>74.43611093599316</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C4" t="n">
-        <v>110.3209530216226</v>
+        <v>81.46444275069608</v>
       </c>
       <c r="D4" t="n">
-        <v>135.8846814925053</v>
+        <v>152.4251668136555</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.55938487390499</v>
+        <v>53.62796834448203</v>
       </c>
       <c r="C5" t="n">
-        <v>256.3097818862361</v>
+        <v>202.1909396896307</v>
       </c>
       <c r="D5" t="n">
-        <v>109.1458010196392</v>
+        <v>133.7385810110218</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.51454327467913</v>
+        <v>42.30449032369931</v>
       </c>
       <c r="C6" t="n">
-        <v>323.7038165396669</v>
+        <v>267.7540148746411</v>
       </c>
       <c r="D6" t="n">
-        <v>56.79508643838223</v>
+        <v>69.11209313586272</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.39085875947725</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>259.9677738322596</v>
+        <v>223.676488197072</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>160.7219166622453</v>
+        <v>144.3659999094935</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>68.00468172547228</v>
+        <v>61.90311974357836</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3131,7 +3131,7 @@
         <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.063633674326795</v>
+        <v>1.942878706704438</v>
       </c>
       <c r="C2" t="n">
-        <v>4.061490252469055</v>
+        <v>2.898119222936584</v>
       </c>
       <c r="D2" t="n">
-        <v>11.11632925518663</v>
+        <v>12.23650338573225</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.849694790259</v>
+        <v>11.83005983617407</v>
       </c>
       <c r="C3" t="n">
-        <v>27.91599597025805</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="D3" t="n">
-        <v>67.85349257901831</v>
+        <v>71.22579594310609</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.56220694383071</v>
+        <v>35.8887690764464</v>
       </c>
       <c r="C4" t="n">
-        <v>95.12055331676922</v>
+        <v>65.99602592258334</v>
       </c>
       <c r="D4" t="n">
-        <v>139.1264124119282</v>
+        <v>156.2412201400629</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.48637569089224</v>
+        <v>57.62859023928778</v>
       </c>
       <c r="C5" t="n">
-        <v>243.5225180384214</v>
+        <v>187.6365299741717</v>
       </c>
       <c r="D5" t="n">
-        <v>123.970191353766</v>
+        <v>147.7775731817512</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.35103337642641</v>
+        <v>50.47557646614552</v>
       </c>
       <c r="C6" t="n">
-        <v>365.3240287135062</v>
+        <v>298.6270349300906</v>
       </c>
       <c r="D6" t="n">
-        <v>66.61649047166733</v>
+        <v>83.28067600355268</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.71403368062369</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>327.6396430859923</v>
+        <v>281.7066132473968</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>44.55563780953724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>205.9510333968959</v>
+        <v>185.506137455956</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>72.22030636750809</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.952516257297659</v>
+        <v>2.651700549170635</v>
       </c>
       <c r="C2" t="n">
-        <v>14.35609667920111</v>
+        <v>15.54499314904399</v>
       </c>
       <c r="D2" t="n">
-        <v>18.90060680215959</v>
+        <v>11.05546089752333</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.552405162321465</v>
+        <v>9.321694451823465</v>
       </c>
       <c r="C3" t="n">
-        <v>22.36421270274234</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="D3" t="n">
-        <v>62.24280444924778</v>
+        <v>65.45802818065609</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.47813649416398</v>
+        <v>29.9158160438088</v>
       </c>
       <c r="C4" t="n">
-        <v>84.0425122220482</v>
+        <v>55.36468003329463</v>
       </c>
       <c r="D4" t="n">
-        <v>139.904938341396</v>
+        <v>155.6541350129233</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.13647259755287</v>
+        <v>56.13142499031139</v>
       </c>
       <c r="C5" t="n">
-        <v>215.1745530782947</v>
+        <v>159.2394776288327</v>
       </c>
       <c r="D5" t="n">
-        <v>136.9292610498239</v>
+        <v>163.8046044535803</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>60.61899374642356</v>
       </c>
       <c r="C6" t="n">
-        <v>374.8234194997983</v>
+        <v>299.5930746710695</v>
       </c>
       <c r="D6" t="n">
-        <v>82.79765613306327</v>
+        <v>102.0379476408923</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>30.12296480940488</v>
       </c>
       <c r="C7" t="n">
-        <v>406.8696280618226</v>
+        <v>342.1322026960837</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>53.41885608347744</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>286.8961316120454</v>
+        <v>260.2760426113931</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>135.3437385074652</v>
+        <v>129.2421765255713</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.599487994396307</v>
+        <v>4.210715903514569</v>
       </c>
       <c r="C2" t="n">
-        <v>10.57931326096363</v>
+        <v>4.680973053848792</v>
       </c>
       <c r="D2" t="n">
-        <v>3.237803928605981</v>
+        <v>4.811545498513618</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.915790681613027</v>
+        <v>1.898700060013331</v>
       </c>
       <c r="C2" t="n">
-        <v>8.498989875664638</v>
+        <v>8.953539062730911</v>
       </c>
       <c r="D2" t="n">
-        <v>14.06157236792706</v>
+        <v>8.136724972797564</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.003248342749</v>
+        <v>12.83144249450581</v>
       </c>
       <c r="C3" t="n">
-        <v>35.29873870619407</v>
+        <v>29.68805057642355</v>
       </c>
       <c r="D3" t="n">
-        <v>69.17394324123026</v>
+        <v>70.39621913301754</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.65002445786518</v>
+        <v>41.95106115017045</v>
       </c>
       <c r="C4" t="n">
-        <v>121.118214272929</v>
+        <v>82.91939284838985</v>
       </c>
       <c r="D4" t="n">
-        <v>141.3343629987793</v>
+        <v>159.4063747385546</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.18245050873644</v>
+        <v>35.68652904937156</v>
       </c>
       <c r="C5" t="n">
-        <v>320.1479263548849</v>
+        <v>245.633275602552</v>
       </c>
       <c r="D5" t="n">
-        <v>122.4975697973958</v>
+        <v>148.4157091895116</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.65789413503238</v>
+        <v>18.67676832559133</v>
       </c>
       <c r="C6" t="n">
-        <v>330.4258430706448</v>
+        <v>284.0559355036594</v>
       </c>
       <c r="D6" t="n">
-        <v>66.61649047166733</v>
+        <v>80.5838150599867</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>201.7579889520577</v>
+        <v>183.0134800348734</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>99.72102305886976</v>
+        <v>95.2148010963769</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.59890715731956</v>
+        <v>5.784457473422207</v>
       </c>
       <c r="C2" t="n">
-        <v>5.810964661436871</v>
+        <v>9.382562809486767</v>
       </c>
       <c r="D2" t="n">
-        <v>8.700248155035233</v>
+        <v>22.12662975831461</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.778207134298231</v>
+        <v>8.953539062730909</v>
       </c>
       <c r="C3" t="n">
-        <v>27.08151042164826</v>
+        <v>11.98223073033232</v>
       </c>
       <c r="D3" t="n">
-        <v>5.856125055832224</v>
+        <v>7.368016520372312</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39884107958524</v>
+        <v>13.3996526937085</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14687388724039</v>
+        <v>70.15112292588569</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576334244657087</v>
+        <v>1.576429728671588</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.592615760466579</v>
+        <v>4.285328729037327</v>
       </c>
       <c r="C2" t="n">
-        <v>5.920920404312514</v>
+        <v>5.524294331796802</v>
       </c>
       <c r="D2" t="n">
-        <v>14.02132071205295</v>
+        <v>21.60041298883832</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.50179625005713</v>
+        <v>15.53615741970577</v>
       </c>
       <c r="C3" t="n">
-        <v>24.54860134469149</v>
+        <v>27.37603473292231</v>
       </c>
       <c r="D3" t="n">
-        <v>11.74661128131309</v>
+        <v>24.17062847855647</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.47368541953247</v>
+        <v>10.54200684820225</v>
       </c>
       <c r="C4" t="n">
-        <v>41.78514578815274</v>
+        <v>18.79948678862217</v>
       </c>
       <c r="D4" t="n">
-        <v>18.13582534055133</v>
+        <v>18.92711399017426</v>
       </c>
     </row>
     <row r="5">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44321256027741</v>
+        <v>15.44365444157393</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15687007312661</v>
+        <v>86.15933530562297</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251202644268929</v>
+        <v>3.251295671910301</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.929936060099982</v>
+        <v>4.090942683596459</v>
       </c>
       <c r="C2" t="n">
-        <v>6.26060510998191</v>
+        <v>5.038329218194631</v>
       </c>
       <c r="D2" t="n">
-        <v>19.0979380907132</v>
+        <v>27.62736214520949</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.73250696055514</v>
+        <v>15.14836707652828</v>
       </c>
       <c r="C3" t="n">
-        <v>23.63557597974196</v>
+        <v>23.81229056650639</v>
       </c>
       <c r="D3" t="n">
-        <v>20.23382018452676</v>
+        <v>35.83869994352981</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.90082778633785</v>
+        <v>21.5307089018368</v>
       </c>
       <c r="C4" t="n">
-        <v>53.39922112939251</v>
+        <v>48.06440410451534</v>
       </c>
       <c r="D4" t="n">
-        <v>19.96089432274615</v>
+        <v>26.77618688562751</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.55378782065321</v>
+        <v>9.817477042468106</v>
       </c>
       <c r="C5" t="n">
-        <v>46.28940425523712</v>
+        <v>22.0402359603409</v>
       </c>
       <c r="D5" t="n">
-        <v>28.98610096788708</v>
+        <v>29.25608158655496</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.65583282863265</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73830688883498</v>
+        <v>16.73907982171565</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1036720218934</v>
+        <v>102.1083869124654</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021492066650493</v>
+        <v>5.021723946514694</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.998478472948011</v>
+        <v>5.549819772107219</v>
       </c>
       <c r="C2" t="n">
-        <v>7.435757111965342</v>
+        <v>7.981608835526568</v>
       </c>
       <c r="D2" t="n">
-        <v>18.40187896840222</v>
+        <v>25.53427603975529</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.49059611468292</v>
+        <v>14.52986602285279</v>
       </c>
       <c r="C3" t="n">
-        <v>24.00373136883452</v>
+        <v>21.34319509032566</v>
       </c>
       <c r="D3" t="n">
-        <v>30.24764676784423</v>
+        <v>48.86158324036376</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.63579696392021</v>
+        <v>25.85727103445249</v>
       </c>
       <c r="C4" t="n">
-        <v>56.61542660850506</v>
+        <v>54.03735713715294</v>
       </c>
       <c r="D4" t="n">
-        <v>25.30847406777853</v>
+        <v>38.07119422298706</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.59844949342983</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="C5" t="n">
-        <v>74.09740797802803</v>
+        <v>58.73305640656545</v>
       </c>
       <c r="D5" t="n">
-        <v>29.42788743479815</v>
+        <v>31.90680038802134</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.18366893615217</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>44.43782808502763</v>
+        <v>24.23149683621978</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
         <v>39.46527596301753</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,7 +5574,7 @@
         <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>46.86470840992573</v>
@@ -5613,7 +5613,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>30.42141611149592</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06553790276218</v>
+        <v>18.06666318940209</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8561282227819</v>
+        <v>117.8634693784803</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882109677242736</v>
+        <v>6.882538357867461</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.700027170856981</v>
+        <v>7.795076771719675</v>
       </c>
       <c r="C2" t="n">
-        <v>13.26242973667016</v>
+        <v>7.898160280665589</v>
       </c>
       <c r="D2" t="n">
-        <v>19.3600647277471</v>
+        <v>22.98860424264331</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.9435827169682</v>
+        <v>15.18272824617692</v>
       </c>
       <c r="C3" t="n">
-        <v>25.17691987540945</v>
+        <v>25.25545969174919</v>
       </c>
       <c r="D3" t="n">
-        <v>35.28401249063037</v>
+        <v>54.0010324720958</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.83326712119406</v>
+        <v>19.61630087855552</v>
       </c>
       <c r="C4" t="n">
-        <v>48.56215019056847</v>
+        <v>44.50360518121217</v>
       </c>
       <c r="D4" t="n">
-        <v>29.9030533236536</v>
+        <v>46.37972504402781</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.02136176978195</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C5" t="n">
-        <v>67.51969835957439</v>
+        <v>60.37748381117885</v>
       </c>
       <c r="D5" t="n">
-        <v>25.57452769562942</v>
+        <v>30.58144098728815</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="C6" t="n">
-        <v>56.11080828852221</v>
+        <v>40.77492740048278</v>
       </c>
       <c r="D6" t="n">
-        <v>30.22899356146354</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>27.42806736124739</v>
+        <v>18.02586959767568</v>
       </c>
       <c r="D7" t="n">
         <v>30.66194429903638</v>
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
         <v>30.37527396939631</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061274449017831</v>
+        <v>7.061852465312957</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19944795954216</v>
+        <v>66.20486686230898</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295955836763373</v>
+        <v>5.296389348984718</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.357978059151591</v>
+        <v>6.388232311533995</v>
       </c>
       <c r="C2" t="n">
-        <v>10.19054117008189</v>
+        <v>6.689628856737766</v>
       </c>
       <c r="D2" t="n">
-        <v>29.16968778858123</v>
+        <v>29.17852351791945</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4666743168825</v>
+        <v>22.60474089028281</v>
       </c>
       <c r="C3" t="n">
-        <v>42.65202901100267</v>
+        <v>28.9468310597172</v>
       </c>
       <c r="D3" t="n">
-        <v>43.45706212848506</v>
+        <v>61.18251692866122</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.99315312826605</v>
+        <v>26.010423676315</v>
       </c>
       <c r="C4" t="n">
-        <v>57.92998678449155</v>
+        <v>56.57713844803943</v>
       </c>
       <c r="D4" t="n">
-        <v>42.05316291141212</v>
+        <v>63.46900733185205</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.35363446217388</v>
+        <v>24.83821691744431</v>
       </c>
       <c r="C5" t="n">
-        <v>81.50960314509145</v>
+        <v>74.12195167063419</v>
       </c>
       <c r="D5" t="n">
-        <v>31.21957699504858</v>
+        <v>41.45429681182157</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.52205309894783</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="C6" t="n">
-        <v>86.86307337634931</v>
+        <v>73.78128521726055</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>59.22785724950582</v>
+        <v>42.22006002113408</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="D8" t="n">
         <v>32.29459073119883</v>
@@ -6168,7 +6168,7 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
         <v>31.17343485294896</v>
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285012314583014</v>
+        <v>7.285284831143382</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58200276379877</v>
+        <v>75.58483012311261</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374385775260137</v>
+        <v>6.37462422725046</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.073672135547516</v>
+        <v>4.867505117655686</v>
       </c>
       <c r="C2" t="n">
-        <v>10.14636252339078</v>
+        <v>8.235881490926493</v>
       </c>
       <c r="D2" t="n">
-        <v>32.9798506287631</v>
+        <v>26.02416814417445</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56208377064369</v>
+        <v>22.33966901013617</v>
       </c>
       <c r="C3" t="n">
-        <v>40.83579575814608</v>
+        <v>27.17968519207295</v>
       </c>
       <c r="D3" t="n">
-        <v>56.710656135817</v>
+        <v>70.32749679372027</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.22586839190155</v>
+        <v>36.05468443846411</v>
       </c>
       <c r="C4" t="n">
-        <v>86.722683454642</v>
+        <v>65.98326320242812</v>
       </c>
       <c r="D4" t="n">
-        <v>54.38195058134357</v>
+        <v>79.89462817160542</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.4285093296039</v>
+        <v>32.83946070705581</v>
       </c>
       <c r="C5" t="n">
-        <v>96.1621876309751</v>
+        <v>91.54797342101507</v>
       </c>
       <c r="D5" t="n">
-        <v>39.02447124381072</v>
+        <v>54.48699758569799</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>26.88810612391165</v>
       </c>
       <c r="C6" t="n">
-        <v>109.726013912849</v>
+        <v>97.40900721536855</v>
       </c>
       <c r="D6" t="n">
-        <v>34.81768233111314</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>96.23778220420208</v>
+        <v>77.91247955673111</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>56.32777453116075</v>
+        <v>40.80634332701867</v>
       </c>
       <c r="D8" t="n">
         <v>34.38080460272329</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6507,7 +6507,7 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.494458786889926</v>
+        <v>7.495406371881531</v>
       </c>
       <c r="C21" t="n">
-        <v>85.2494687008729</v>
+        <v>85.26024748015242</v>
       </c>
       <c r="D21" t="n">
-        <v>7.494458786889926</v>
+        <v>7.495406371881531</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_37_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497650955917</v>
+        <v>10.84497633736499</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789072559861</v>
+        <v>37.78907195985433</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.060328578315561</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C2" t="n">
-        <v>7.268860002243384</v>
+        <v>5.905212441044564</v>
       </c>
       <c r="D2" t="n">
-        <v>26.29316701513807</v>
+        <v>23.1162314441954</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.22752878767378</v>
+        <v>14.21079801897258</v>
       </c>
       <c r="C3" t="n">
-        <v>29.79113408536946</v>
+        <v>32.12278488295564</v>
       </c>
       <c r="D3" t="n">
-        <v>74.09740797802802</v>
+        <v>64.05903770210438</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.46233071990478</v>
+        <v>30.70710469343173</v>
       </c>
       <c r="C4" t="n">
-        <v>66.40443296755001</v>
+        <v>75.61911691961056</v>
       </c>
       <c r="D4" t="n">
-        <v>94.48241730900878</v>
+        <v>83.34056261351174</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.58959806855839</v>
+        <v>39.1226460142354</v>
       </c>
       <c r="C5" t="n">
-        <v>107.6240920780566</v>
+        <v>107.0104997629024</v>
       </c>
       <c r="D5" t="n">
-        <v>69.94952392758525</v>
+        <v>64.37810570598461</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.54221213684728</v>
+        <v>36.91076843656734</v>
       </c>
       <c r="C6" t="n">
-        <v>121.2379874928471</v>
+        <v>131.0593915261322</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>46.36990756698535</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>26.11056194214817</v>
       </c>
       <c r="C7" t="n">
-        <v>110.6704552043344</v>
+        <v>131.5109954700857</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>13.4352173326176</v>
       </c>
       <c r="C8" t="n">
-        <v>72.60024272905163</v>
+        <v>92.71134445054753</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>38.60624672180155</v>
+        <v>51.47499562906875</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691090784944786</v>
+        <v>7.673827573012028</v>
       </c>
       <c r="C21" t="n">
-        <v>94.21586211557363</v>
+        <v>93.04515932277084</v>
       </c>
       <c r="D21" t="n">
-        <v>8.652477133062884</v>
+        <v>7.673827573012028</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.876741757621406</v>
+        <v>6.550220682734719</v>
       </c>
       <c r="C2" t="n">
-        <v>11.95376004690916</v>
+        <v>12.89525609528186</v>
       </c>
       <c r="D2" t="n">
-        <v>24.14510303824605</v>
+        <v>23.85057872697201</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.67913273162732</v>
+        <v>14.60349710067131</v>
       </c>
       <c r="C3" t="n">
-        <v>28.83393007372882</v>
+        <v>27.29749491658256</v>
       </c>
       <c r="D3" t="n">
-        <v>76.91993262773759</v>
+        <v>66.7588438887831</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.05843150283185</v>
+        <v>28.60125586782233</v>
       </c>
       <c r="C4" t="n">
-        <v>70.32258805519903</v>
+        <v>77.03577885683872</v>
       </c>
       <c r="D4" t="n">
-        <v>107.6280190688736</v>
+        <v>94.38031554776711</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.41274461307373</v>
+        <v>42.16606389740051</v>
       </c>
       <c r="C5" t="n">
-        <v>113.588209381356</v>
+        <v>122.4730261047896</v>
       </c>
       <c r="D5" t="n">
-        <v>84.30758410219485</v>
+        <v>76.52723354603889</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.08814597586652</v>
+        <v>44.59883470852411</v>
       </c>
       <c r="C6" t="n">
-        <v>144.9462128027034</v>
+        <v>148.1260936167588</v>
       </c>
       <c r="D6" t="n">
-        <v>56.51332484726341</v>
+        <v>54.82275530055039</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.93763547748049</v>
+        <v>34.19525428662065</v>
       </c>
       <c r="C7" t="n">
-        <v>140.2544405241078</v>
+        <v>158.1605369018654</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>43.11835917051991</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.19316761802514</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C8" t="n">
-        <v>107.7320843255237</v>
+        <v>131.6818195706247</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>10.20624913334984</v>
       </c>
       <c r="C9" t="n">
-        <v>62.01405723415825</v>
+        <v>80.42968067041991</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>37.72365553568369</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.871474008735873</v>
+        <v>7.852028543988703</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3291621135664</v>
+        <v>101.0948675038545</v>
       </c>
       <c r="D21" t="n">
-        <v>9.839342510919842</v>
+        <v>8.83353211198729</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.366053024963819</v>
+        <v>6.989061906533043</v>
       </c>
       <c r="C2" t="n">
-        <v>9.959830459583891</v>
+        <v>10.80413348523615</v>
       </c>
       <c r="D2" t="n">
-        <v>28.79171492244621</v>
+        <v>30.26139123570368</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.32570355809846</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="C3" t="n">
-        <v>36.93825737228624</v>
+        <v>37.62057202673778</v>
       </c>
       <c r="D3" t="n">
-        <v>78.21583959734339</v>
+        <v>68.78124415953154</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.98636300979434</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="C4" t="n">
-        <v>70.90967318233861</v>
+        <v>72.0710807164626</v>
       </c>
       <c r="D4" t="n">
-        <v>116.6129740581404</v>
+        <v>101.9996594804266</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.86711387369075</v>
+        <v>42.19060759000669</v>
       </c>
       <c r="C5" t="n">
-        <v>119.2578023733813</v>
+        <v>130.7687942056752</v>
       </c>
       <c r="D5" t="n">
-        <v>98.59201319898595</v>
+        <v>89.31449739385359</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.58753676215866</v>
+        <v>49.54978838104078</v>
       </c>
       <c r="C6" t="n">
-        <v>160.684610249484</v>
+        <v>166.6016036629795</v>
       </c>
       <c r="D6" t="n">
-        <v>67.50202690089796</v>
+        <v>63.03409309887072</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.9206269713388</v>
+        <v>41.98051358129786</v>
       </c>
       <c r="C7" t="n">
-        <v>169.0598999144135</v>
+        <v>181.516314785897</v>
       </c>
       <c r="D7" t="n">
-        <v>47.49008169753095</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.03594911662541</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C8" t="n">
-        <v>140.9446091601933</v>
+        <v>166.3964183927919</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7562488319063</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>92.96561710594743</v>
+        <v>114.8203027501857</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1517,7 +1517,7 @@
         <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>52.3860574986098</v>
+        <v>66.05198554172541</v>
       </c>
       <c r="D10" t="n">
         <v>36.44247478164161</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>41.5809422656694</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
         <v>33.62976760897449</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.036138863555019</v>
+        <v>8.014315854951684</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4969093738815</v>
+        <v>109.1950535237167</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04969093738815</v>
+        <v>10.01789481868961</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.757369448330795</v>
+        <v>6.386268816125502</v>
       </c>
       <c r="C2" t="n">
-        <v>6.772095663894499</v>
+        <v>7.432811868852601</v>
       </c>
       <c r="D2" t="n">
-        <v>23.63361248433347</v>
+        <v>24.86865109627595</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.30316441862979</v>
+        <v>20.24363766156923</v>
       </c>
       <c r="C3" t="n">
-        <v>52.69039928692631</v>
+        <v>53.60833339039709</v>
       </c>
       <c r="D3" t="n">
-        <v>85.85874547490481</v>
+        <v>74.77972263247955</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.39781310886498</v>
+        <v>20.26719960647115</v>
       </c>
       <c r="C4" t="n">
-        <v>98.32399607572655</v>
+        <v>104.7053561533308</v>
       </c>
       <c r="D4" t="n">
-        <v>111.5589368766778</v>
+        <v>98.6813522400724</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>27.90617849321559</v>
       </c>
       <c r="C5" t="n">
-        <v>96.01492547533807</v>
+        <v>99.54921721062659</v>
       </c>
       <c r="D5" t="n">
-        <v>66.83247496660162</v>
+        <v>61.6537558266997</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.00256969468102</v>
+        <v>26.04282135055514</v>
       </c>
       <c r="C6" t="n">
-        <v>111.3360801478138</v>
+        <v>119.5474179461341</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>99.11233948223673</v>
+        <v>117.0184358599943</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>68.51126354086365</v>
+        <v>84.61683462903258</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1814,7 +1814,7 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>39.93749660876023</v>
+        <v>50.36562072326985</v>
       </c>
       <c r="D9" t="n">
         <v>27.73437264497238</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,7 +1839,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
         <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.070325981807276</v>
+        <v>3.751257977927062</v>
       </c>
       <c r="C2" t="n">
-        <v>3.218168974521045</v>
+        <v>3.455751918948773</v>
       </c>
       <c r="D2" t="n">
-        <v>16.21847207415731</v>
+        <v>18.00328940047801</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.47497026687298</v>
+        <v>21.59844949342983</v>
       </c>
       <c r="C3" t="n">
-        <v>40.11421119552467</v>
+        <v>41.92062697133881</v>
       </c>
       <c r="D3" t="n">
-        <v>85.30405802200535</v>
+        <v>77.92622402459057</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52315801983909</v>
+        <v>28.19284882285566</v>
       </c>
       <c r="C4" t="n">
-        <v>116.9192793418654</v>
+        <v>122.5221134900019</v>
       </c>
       <c r="D4" t="n">
-        <v>127.4612861900676</v>
+        <v>110.410292062709</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.56381058634071</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="C5" t="n">
-        <v>137.0274358202486</v>
+        <v>142.3288734231814</v>
       </c>
       <c r="D5" t="n">
-        <v>84.50393364304422</v>
+        <v>76.94447632034378</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.35603992593888</v>
+        <v>30.87302005544945</v>
       </c>
       <c r="C6" t="n">
-        <v>132.9512193522158</v>
+        <v>141.9273386121444</v>
       </c>
       <c r="D6" t="n">
-        <v>39.32586778901449</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>126.0613139638117</v>
+        <v>143.3685442419787</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>90.12443924985719</v>
+        <v>108.9003640935774</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>45.26249615659493</v>
+        <v>55.57968278052466</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>20.82875929330033</v>
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.98000519301657</v>
+        <v>4.518002934943821</v>
       </c>
       <c r="C2" t="n">
-        <v>4.565126824747668</v>
+        <v>4.905793278121311</v>
       </c>
       <c r="D2" t="n">
-        <v>21.01136436629024</v>
+        <v>18.65713337150638</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.30115986549229</v>
+        <v>17.15604113171301</v>
       </c>
       <c r="C3" t="n">
-        <v>25.55980148006571</v>
+        <v>26.76735115628928</v>
       </c>
       <c r="D3" t="n">
-        <v>78.9963290222196</v>
+        <v>74.33302742704726</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.16428032844126</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="C4" t="n">
-        <v>108.3044432370996</v>
+        <v>113.345717698407</v>
       </c>
       <c r="D4" t="n">
-        <v>138.9732597700657</v>
+        <v>122.0881810047248</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.07418052382881</v>
+        <v>36.00559705325178</v>
       </c>
       <c r="C5" t="n">
-        <v>175.4628584415112</v>
+        <v>184.6176557836127</v>
       </c>
       <c r="D5" t="n">
-        <v>106.5932569885975</v>
+        <v>95.37678946757764</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08435785376978</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>174.3299215908104</v>
+        <v>180.931193154166</v>
       </c>
       <c r="D6" t="n">
-        <v>53.09193409796327</v>
+        <v>50.83784136901259</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>158.1605369018654</v>
+        <v>173.910715321097</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>125.2562808463293</v>
+        <v>146.368765226157</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>89.30467991681108</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>25.38505038870978</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2579,7 +2579,7 @@
         <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.372884201164541</v>
+        <v>2.686061718819273</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1392282475538</v>
+        <v>2.324778563656447</v>
       </c>
       <c r="D2" t="n">
-        <v>14.67810992619406</v>
+        <v>13.01797455831271</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.92318699935727</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="C3" t="n">
-        <v>23.86137795171873</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D3" t="n">
-        <v>79.9338980797753</v>
+        <v>74.63736921536376</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.91652005407257</v>
+        <v>37.95632974159018</v>
       </c>
       <c r="C4" t="n">
-        <v>102.7781854098943</v>
+        <v>108.6745621216007</v>
       </c>
       <c r="D4" t="n">
-        <v>147.677434915918</v>
+        <v>130.8561697513531</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.1541029985003</v>
+        <v>37.52730599483434</v>
       </c>
       <c r="C5" t="n">
-        <v>210.2412708644545</v>
+        <v>218.7824758914017</v>
       </c>
       <c r="D5" t="n">
-        <v>112.4837432140783</v>
+        <v>100.7273144557228</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.03402667894593</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>207.7387959663294</v>
+        <v>219.0092596110827</v>
       </c>
       <c r="D6" t="n">
-        <v>52.00513938936205</v>
+        <v>49.99255659565609</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.785259294677205</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>166.1254560264198</v>
+        <v>185.1693979933994</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>92.12720456652069</v>
+        <v>110.2355409713531</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
         <v>20.25738212942868</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2876,7 +2876,7 @@
         <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.606540154775282</v>
+        <v>2.676244241776805</v>
       </c>
       <c r="C2" t="n">
-        <v>4.487568756112171</v>
+        <v>4.966661635784614</v>
       </c>
       <c r="D2" t="n">
-        <v>16.29210315197582</v>
+        <v>15.99659709299753</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.72483290537041</v>
+        <v>13.64138435050943</v>
       </c>
       <c r="C3" t="n">
-        <v>15.9583089325319</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="D3" t="n">
-        <v>74.43611093599316</v>
+        <v>69.0364985626357</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.29190752999335</v>
+        <v>36.37375244234432</v>
       </c>
       <c r="C4" t="n">
-        <v>81.46444275069608</v>
+        <v>87.15661593991908</v>
       </c>
       <c r="D4" t="n">
-        <v>152.4251668136555</v>
+        <v>136.5738683808866</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.62796834448203</v>
+        <v>45.67581194008286</v>
       </c>
       <c r="C5" t="n">
-        <v>202.1909396896307</v>
+        <v>211.9838730394926</v>
       </c>
       <c r="D5" t="n">
-        <v>133.7385810110218</v>
+        <v>119.3805208364122</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.30449032369931</v>
+        <v>37.71580155404972</v>
       </c>
       <c r="C6" t="n">
-        <v>267.7540148746411</v>
+        <v>276.8911407580662</v>
       </c>
       <c r="D6" t="n">
-        <v>69.11209313586272</v>
+        <v>64.80516595733197</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.18745705824891</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>223.676488197072</v>
+        <v>242.001790844543</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>144.3659999094935</v>
+        <v>166.9805582768187</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>61.90311974357836</v>
+        <v>71.55468142402876</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3103,7 +3103,7 @@
         <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.942878706704438</v>
+        <v>1.964477156197868</v>
       </c>
       <c r="C2" t="n">
-        <v>2.898119222936584</v>
+        <v>2.957024085191393</v>
       </c>
       <c r="D2" t="n">
-        <v>12.23650338573225</v>
+        <v>11.84282255632927</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.83005983617407</v>
+        <v>11.87914722138641</v>
       </c>
       <c r="C3" t="n">
-        <v>16.95969159086365</v>
+        <v>18.19669369821463</v>
       </c>
       <c r="D3" t="n">
-        <v>71.22579594310609</v>
+        <v>67.25462647942776</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.8887690764464</v>
+        <v>33.23412328416303</v>
       </c>
       <c r="C4" t="n">
-        <v>65.99602592258334</v>
+        <v>70.51402885752717</v>
       </c>
       <c r="D4" t="n">
-        <v>156.2412201400629</v>
+        <v>139.0881242514626</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.62859023928778</v>
+        <v>50.24093876483053</v>
       </c>
       <c r="C5" t="n">
-        <v>187.6365299741717</v>
+        <v>199.932919969863</v>
       </c>
       <c r="D5" t="n">
-        <v>147.7775731817512</v>
+        <v>132.0205225285899</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.47557646614552</v>
+        <v>43.9548082145382</v>
       </c>
       <c r="C6" t="n">
-        <v>298.6270349300906</v>
+        <v>309.6559886395993</v>
       </c>
       <c r="D6" t="n">
-        <v>83.28067600355268</v>
+        <v>77.24292762243481</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>281.7066132473968</v>
+        <v>298.4748640359323</v>
       </c>
       <c r="D7" t="n">
-        <v>44.55563780953724</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>185.506137455956</v>
+        <v>209.288975591335</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>72.22030636750809</v>
+        <v>80.87343063273947</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.651700549170635</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C2" t="n">
-        <v>15.54499314904399</v>
+        <v>9.557313900842699</v>
       </c>
       <c r="D2" t="n">
-        <v>11.05546089752333</v>
+        <v>21.70545999319273</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.321694451823465</v>
+        <v>9.405143006684444</v>
       </c>
       <c r="C3" t="n">
-        <v>14.21570675749381</v>
+        <v>14.98637870532756</v>
       </c>
       <c r="D3" t="n">
-        <v>65.45802818065609</v>
+        <v>61.98264130762237</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.9158160438088</v>
+        <v>28.18008610270045</v>
       </c>
       <c r="C4" t="n">
-        <v>55.36468003329463</v>
+        <v>59.24454696047802</v>
       </c>
       <c r="D4" t="n">
-        <v>155.6541350129233</v>
+        <v>140.0070401026376</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.13142499031139</v>
+        <v>49.99550183876883</v>
       </c>
       <c r="C5" t="n">
-        <v>159.2394776288327</v>
+        <v>169.817809142092</v>
       </c>
       <c r="D5" t="n">
-        <v>163.8046044535803</v>
+        <v>146.2067768549562</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.61899374642356</v>
+        <v>52.81017250684443</v>
       </c>
       <c r="C6" t="n">
-        <v>299.5930746710695</v>
+        <v>314.0434191298783</v>
       </c>
       <c r="D6" t="n">
-        <v>102.0379476408923</v>
+        <v>93.62535156320133</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.12296480940488</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="C7" t="n">
-        <v>342.1322026960837</v>
+        <v>361.6552375427357</v>
       </c>
       <c r="D7" t="n">
-        <v>53.41885608347744</v>
+        <v>51.50248456478767</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>260.2760426113931</v>
+        <v>280.0533501134451</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>129.2421765255713</v>
+        <v>145.4390501502352</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>54.52135875534661</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.210715903514569</v>
+        <v>4.403138453546944</v>
       </c>
       <c r="C2" t="n">
-        <v>4.680973053848792</v>
+        <v>11.72697632722815</v>
       </c>
       <c r="D2" t="n">
-        <v>4.811545498513618</v>
+        <v>13.99383177633403</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.898700060013331</v>
+        <v>1.726894211770139</v>
       </c>
       <c r="C2" t="n">
-        <v>8.953539062730911</v>
+        <v>5.504659377711866</v>
       </c>
       <c r="D2" t="n">
-        <v>8.136724972797564</v>
+        <v>16.14876798715579</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.83144249450581</v>
+        <v>12.47310458245573</v>
       </c>
       <c r="C3" t="n">
-        <v>29.68805057642355</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D3" t="n">
-        <v>70.39621913301754</v>
+        <v>69.19848693383643</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.95106115017045</v>
+        <v>38.41578766717769</v>
       </c>
       <c r="C4" t="n">
-        <v>82.91939284838985</v>
+        <v>88.58604059730244</v>
       </c>
       <c r="D4" t="n">
-        <v>159.4063747385546</v>
+        <v>143.2360083019054</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.68652904937156</v>
+        <v>30.65507206510666</v>
       </c>
       <c r="C5" t="n">
-        <v>245.633275602552</v>
+        <v>261.2185204074701</v>
       </c>
       <c r="D5" t="n">
-        <v>148.4157091895116</v>
+        <v>133.2231634662922</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.67676832559133</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="C6" t="n">
-        <v>284.0559355036594</v>
+        <v>296.6547037922588</v>
       </c>
       <c r="D6" t="n">
-        <v>80.5838150599867</v>
+        <v>75.35109979635121</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>183.0134800348734</v>
+        <v>196.9071735453743</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>95.2148010963769</v>
+        <v>107.1479444414969</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
         <v>19.21771131063132</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
         <v>16.34806277111788</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.784457473422207</v>
+        <v>6.66999390265283</v>
       </c>
       <c r="C2" t="n">
-        <v>9.382562809486767</v>
+        <v>5.276893910326605</v>
       </c>
       <c r="D2" t="n">
-        <v>22.12662975831461</v>
+        <v>13.91431021229004</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.953539062730909</v>
+        <v>9.360964359993337</v>
       </c>
       <c r="C3" t="n">
-        <v>11.98223073033232</v>
+        <v>29.55060589782899</v>
       </c>
       <c r="D3" t="n">
-        <v>7.368016520372312</v>
+        <v>14.89311267342411</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3996526937085</v>
+        <v>13.39683224642141</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15112292588569</v>
+        <v>70.13635705479443</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576429728671588</v>
+        <v>1.576097911343695</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.285328729037327</v>
+        <v>4.546473618366979</v>
       </c>
       <c r="C2" t="n">
-        <v>5.524294331796802</v>
+        <v>6.566910393706914</v>
       </c>
       <c r="D2" t="n">
-        <v>21.60041298883832</v>
+        <v>16.51495988083985</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.53615741970577</v>
+        <v>17.5143790437631</v>
       </c>
       <c r="C3" t="n">
-        <v>27.37603473292231</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D3" t="n">
-        <v>24.17062847855647</v>
+        <v>22.98271375641783</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.54200684820225</v>
+        <v>11.00146477378976</v>
       </c>
       <c r="C4" t="n">
-        <v>18.79948678862217</v>
+        <v>45.57567367424968</v>
       </c>
       <c r="D4" t="n">
-        <v>18.92711399017426</v>
+        <v>22.8707945181337</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44365444157393</v>
+        <v>15.43777718188133</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15933530562297</v>
+        <v>86.12654638312742</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251295671910301</v>
+        <v>3.25005835408028</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.090942683596459</v>
+        <v>4.292200962967055</v>
       </c>
       <c r="C2" t="n">
-        <v>5.038329218194631</v>
+        <v>6.326382206166446</v>
       </c>
       <c r="D2" t="n">
-        <v>27.62736214520949</v>
+        <v>19.22262004915255</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.14836707652828</v>
+        <v>16.51790512395258</v>
       </c>
       <c r="C3" t="n">
-        <v>23.81229056650639</v>
+        <v>25.14746744428205</v>
       </c>
       <c r="D3" t="n">
-        <v>35.83869994352981</v>
+        <v>30.86123908299849</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.5307089018368</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="C4" t="n">
-        <v>48.06440410451534</v>
+        <v>53.46303473016855</v>
       </c>
       <c r="D4" t="n">
-        <v>26.77618688562751</v>
+        <v>29.25215459573796</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.817477042468106</v>
+        <v>9.989282890711298</v>
       </c>
       <c r="C5" t="n">
-        <v>22.0402359603409</v>
+        <v>50.33911353525522</v>
       </c>
       <c r="D5" t="n">
-        <v>29.25608158655496</v>
+        <v>30.87596529856219</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5302,10 +5302,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73907982171565</v>
+        <v>16.72802563378873</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1083869124654</v>
+        <v>102.0409563661113</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021723946514694</v>
+        <v>4.182006408447183</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.549819772107219</v>
+        <v>4.82921695719006</v>
       </c>
       <c r="C2" t="n">
-        <v>7.981608835526568</v>
+        <v>5.830599615521806</v>
       </c>
       <c r="D2" t="n">
-        <v>25.53427603975529</v>
+        <v>24.09208866221672</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.52986602285279</v>
+        <v>15.4968875115359</v>
       </c>
       <c r="C3" t="n">
-        <v>21.34319509032566</v>
+        <v>24.78912953223196</v>
       </c>
       <c r="D3" t="n">
-        <v>48.86158324036376</v>
+        <v>38.60231973098459</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.85727103445249</v>
+        <v>28.05245890114836</v>
       </c>
       <c r="C4" t="n">
-        <v>54.03735713715294</v>
+        <v>58.74680087442488</v>
       </c>
       <c r="D4" t="n">
-        <v>38.07119422298706</v>
+        <v>37.66278717802039</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.93576979306323</v>
+        <v>22.92380889416302</v>
       </c>
       <c r="C5" t="n">
-        <v>58.73305640656545</v>
+        <v>76.47814616082654</v>
       </c>
       <c r="D5" t="n">
-        <v>31.90680038802134</v>
+        <v>34.01755795215198</v>
       </c>
     </row>
     <row r="6">
@@ -5504,10 +5504,10 @@
         <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>24.23149683621978</v>
+        <v>47.0944373727195</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5613,10 +5613,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06666318940209</v>
+        <v>18.04905996138355</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8634693784803</v>
+        <v>117.7486292718832</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882538357867461</v>
+        <v>6.016353320461183</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.795076771719675</v>
+        <v>5.608724634362028</v>
       </c>
       <c r="C2" t="n">
-        <v>7.898160280665589</v>
+        <v>8.955502558139404</v>
       </c>
       <c r="D2" t="n">
-        <v>22.98860424264331</v>
+        <v>26.06343805234432</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.18272824617692</v>
+        <v>14.31388152791849</v>
       </c>
       <c r="C3" t="n">
-        <v>25.25545969174919</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D3" t="n">
-        <v>54.0010324720958</v>
+        <v>45.46473618366979</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.61630087855552</v>
+        <v>21.22440361811179</v>
       </c>
       <c r="C4" t="n">
-        <v>44.50360518121217</v>
+        <v>50.14472748981433</v>
       </c>
       <c r="D4" t="n">
-        <v>46.37972504402781</v>
+        <v>41.82343394861837</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.33413837680919</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C5" t="n">
-        <v>60.37748381117885</v>
+        <v>69.60591223109887</v>
       </c>
       <c r="D5" t="n">
-        <v>30.58144098728815</v>
+        <v>31.80862561759666</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.54593383901924</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>40.77492740048278</v>
+        <v>57.47936458824226</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>31.47679489356124</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>18.02586959767568</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061852465312957</v>
+        <v>7.052106139284721</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20486686230898</v>
+        <v>66.11349505579426</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296389348984718</v>
+        <v>4.407566337052951</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.388232311533995</v>
+        <v>4.268639018065131</v>
       </c>
       <c r="C2" t="n">
-        <v>6.689628856737766</v>
+        <v>9.000662952534757</v>
       </c>
       <c r="D2" t="n">
-        <v>29.17852351791945</v>
+        <v>21.56703356689393</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.60474089028281</v>
+        <v>17.51928778228433</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9468310597172</v>
+        <v>30.41945261608742</v>
       </c>
       <c r="D3" t="n">
-        <v>61.18251692866122</v>
+        <v>56.37195317785186</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.010423676315</v>
+        <v>25.34676222824415</v>
       </c>
       <c r="C4" t="n">
-        <v>56.57713844803943</v>
+        <v>53.5396110510998</v>
       </c>
       <c r="D4" t="n">
-        <v>63.46900733185205</v>
+        <v>55.54335811546755</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.83821691744431</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="C5" t="n">
-        <v>74.12195167063419</v>
+        <v>83.86579763528378</v>
       </c>
       <c r="D5" t="n">
-        <v>41.45429681182157</v>
+        <v>40.61981126321179</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.91827826083604</v>
+        <v>20.00507296943726</v>
       </c>
       <c r="C6" t="n">
-        <v>73.78128521726055</v>
+        <v>88.87565617005527</v>
       </c>
       <c r="D6" t="n">
-        <v>33.73088762251191</v>
+        <v>34.97868895460962</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>42.22006002113408</v>
+        <v>60.42558944868693</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>22.19731559302038</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285284831143382</v>
+        <v>7.272688717195861</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58483012311261</v>
+        <v>75.45414544090706</v>
       </c>
       <c r="D21" t="n">
-        <v>6.37462422725046</v>
+        <v>5.454516537896895</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.867505117655686</v>
+        <v>3.735550014659113</v>
       </c>
       <c r="C2" t="n">
-        <v>8.235881490926493</v>
+        <v>8.02382398680918</v>
       </c>
       <c r="D2" t="n">
-        <v>26.02416814417445</v>
+        <v>22.78047372934299</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.33966901013617</v>
+        <v>15.97794388661684</v>
       </c>
       <c r="C3" t="n">
-        <v>27.17968519207295</v>
+        <v>33.50214040742241</v>
       </c>
       <c r="D3" t="n">
-        <v>70.32749679372027</v>
+        <v>60.54438092090079</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.05468443846411</v>
+        <v>30.45185029032756</v>
       </c>
       <c r="C4" t="n">
-        <v>65.98326320242812</v>
+        <v>66.13641584429062</v>
       </c>
       <c r="D4" t="n">
-        <v>79.89462817160542</v>
+        <v>71.3308429474605</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.83946070705581</v>
+        <v>33.011266555299</v>
       </c>
       <c r="C5" t="n">
-        <v>91.54797342101507</v>
+        <v>92.55426481786806</v>
       </c>
       <c r="D5" t="n">
-        <v>54.48699758569799</v>
+        <v>51.05088062083415</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.88810612391165</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C6" t="n">
-        <v>97.40900721536855</v>
+        <v>113.5499212208904</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>40.25165587411923</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>77.91247955673111</v>
+        <v>97.07619474362885</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>40.80634332701867</v>
+        <v>57.49605429921444</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.40312275801371</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495406371881531</v>
+        <v>7.480503572793667</v>
       </c>
       <c r="C21" t="n">
-        <v>85.26024748015242</v>
+        <v>84.15566519392875</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495406371881531</v>
+        <v>6.545440626194459</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_37_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_37_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497633736499</v>
+        <v>10.84497640728836</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907195985433</v>
+        <v>37.78907220350069</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.551382356888213</v>
+        <v>1.262527547661398</v>
       </c>
       <c r="C2" t="n">
-        <v>5.905212441044564</v>
+        <v>1.709222753093697</v>
       </c>
       <c r="D2" t="n">
-        <v>23.1162314441954</v>
+        <v>7.643887625265665</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.21079801897258</v>
+        <v>9.650579932746147</v>
       </c>
       <c r="C3" t="n">
-        <v>32.12278488295564</v>
+        <v>26.39919576719673</v>
       </c>
       <c r="D3" t="n">
-        <v>64.05903770210438</v>
+        <v>47.67857725674634</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.70710469343173</v>
+        <v>14.02622945057418</v>
       </c>
       <c r="C4" t="n">
-        <v>75.61911691961056</v>
+        <v>96.80523237725674</v>
       </c>
       <c r="D4" t="n">
-        <v>83.34056261351174</v>
+        <v>66.57034832956771</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.1226460142354</v>
+        <v>10.84831213192726</v>
       </c>
       <c r="C5" t="n">
-        <v>107.0104997629024</v>
+        <v>106.4214511403543</v>
       </c>
       <c r="D5" t="n">
-        <v>64.37810570598461</v>
+        <v>44.98858854711009</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.91076843656734</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>131.0593915261322</v>
+        <v>62.18880832551422</v>
       </c>
       <c r="D6" t="n">
-        <v>46.36990756698535</v>
+        <v>29.90698031447059</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.11056194214817</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>131.5109954700857</v>
+        <v>38.92629647338602</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>29.94330497952771</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>92.71134445054753</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47499562906875</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.673827573012028</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.04515932277084</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.673827573012028</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.550220682734719</v>
+        <v>0.9699667317958486</v>
       </c>
       <c r="C2" t="n">
-        <v>12.89525609528186</v>
+        <v>8.320311793491719</v>
       </c>
       <c r="D2" t="n">
-        <v>23.85057872697201</v>
+        <v>10.84438514111027</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.60349710067131</v>
+        <v>6.74951546669682</v>
       </c>
       <c r="C3" t="n">
-        <v>27.29749491658256</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D3" t="n">
-        <v>66.7588438887831</v>
+        <v>42.73056882734242</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.60125586782233</v>
+        <v>16.83402788472006</v>
       </c>
       <c r="C4" t="n">
-        <v>77.03577885683872</v>
+        <v>79.76700097005333</v>
       </c>
       <c r="D4" t="n">
-        <v>94.38031554776711</v>
+        <v>75.55530331883452</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.16606389740051</v>
+        <v>16.14974973486003</v>
       </c>
       <c r="C5" t="n">
-        <v>122.4730261047896</v>
+        <v>147.0658060961722</v>
       </c>
       <c r="D5" t="n">
-        <v>76.52723354603889</v>
+        <v>58.75760009917161</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.59883470852411</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>148.1260936167588</v>
+        <v>120.3121994077424</v>
       </c>
       <c r="D6" t="n">
-        <v>54.82275530055039</v>
+        <v>37.07177506006381</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.19525428662065</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>158.1605369018654</v>
+        <v>66.05493078483815</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11835917051991</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.11110172149591</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>131.6818195706247</v>
+        <v>41.47393176590651</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.20624913334984</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>80.42968067041991</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>35.73070769606267</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.27040689149115</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.852028543988703</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0948675038545</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.83353211198729</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.989061906533043</v>
+        <v>0.4987278337573797</v>
       </c>
       <c r="C2" t="n">
-        <v>10.80413348523615</v>
+        <v>3.295727043156542</v>
       </c>
       <c r="D2" t="n">
-        <v>30.26139123570368</v>
+        <v>7.320892630568465</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.79417713947344</v>
+        <v>5.939573610693203</v>
       </c>
       <c r="C3" t="n">
-        <v>37.62057202673778</v>
+        <v>24.90203051822035</v>
       </c>
       <c r="D3" t="n">
-        <v>68.78124415953154</v>
+        <v>43.03491061565893</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.55471281509523</v>
+        <v>18.55699510567321</v>
       </c>
       <c r="C4" t="n">
-        <v>72.0710807164626</v>
+        <v>69.14841780091984</v>
       </c>
       <c r="D4" t="n">
-        <v>101.9996594804266</v>
+        <v>80.97945938479815</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.19060759000669</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="C5" t="n">
-        <v>130.7687942056752</v>
+        <v>165.5717503212246</v>
       </c>
       <c r="D5" t="n">
-        <v>89.31449739385359</v>
+        <v>66.53795065532759</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.54978838104078</v>
+        <v>9.982410656781569</v>
       </c>
       <c r="C6" t="n">
-        <v>166.6016036629795</v>
+        <v>161.1676301199734</v>
       </c>
       <c r="D6" t="n">
-        <v>63.03409309887072</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.98051358129786</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>181.516314785897</v>
+        <v>66.59391027446964</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.12078032981814</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>166.3964183927919</v>
+        <v>41.47393176590651</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.42187377538564</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>114.8203027501857</v>
+        <v>27.17968519207294</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>66.05198554172541</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>41.5809422656694</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.014315854951684</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1950535237167</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01789481868961</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.386268816125502</v>
+        <v>0.7068583470577035</v>
       </c>
       <c r="C2" t="n">
-        <v>7.432811868852601</v>
+        <v>2.891246989006857</v>
       </c>
       <c r="D2" t="n">
-        <v>24.86865109627595</v>
+        <v>12.93747124656447</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.24363766156923</v>
+        <v>3.686462629446773</v>
       </c>
       <c r="C3" t="n">
-        <v>53.60833339039709</v>
+        <v>17.92180434102552</v>
       </c>
       <c r="D3" t="n">
-        <v>74.77972263247955</v>
+        <v>39.31899555508476</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.26719960647115</v>
+        <v>15.21316242500857</v>
       </c>
       <c r="C4" t="n">
-        <v>104.7053561533308</v>
+        <v>65.9577377621177</v>
       </c>
       <c r="D4" t="n">
-        <v>98.6813522400724</v>
+        <v>84.14461398328987</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.90617849321559</v>
+        <v>21.96660488252239</v>
       </c>
       <c r="C5" t="n">
-        <v>99.54921721062659</v>
+        <v>146.8203691701105</v>
       </c>
       <c r="D5" t="n">
-        <v>61.6537558266997</v>
+        <v>79.91426312569038</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.04282135055514</v>
+        <v>15.41638419978766</v>
       </c>
       <c r="C6" t="n">
-        <v>119.5474179461341</v>
+        <v>216.6344119145097</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>49.50953672516665</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>117.0184358599943</v>
+        <v>147.6204935490717</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>84.61683462903258</v>
+        <v>63.83814446864884</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>50.36562072326985</v>
+        <v>38.60624672180155</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.751257977927062</v>
+        <v>0.4898921044191584</v>
       </c>
       <c r="C2" t="n">
-        <v>3.455751918948773</v>
+        <v>2.3699389580518</v>
       </c>
       <c r="D2" t="n">
-        <v>18.00328940047801</v>
+        <v>8.758171269585795</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.59844949342983</v>
+        <v>3.166136346195964</v>
       </c>
       <c r="C3" t="n">
-        <v>41.92062697133881</v>
+        <v>14.5593184539802</v>
       </c>
       <c r="D3" t="n">
-        <v>77.92622402459057</v>
+        <v>41.01741908343174</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.19284882285566</v>
+        <v>12.21392318853457</v>
       </c>
       <c r="C4" t="n">
-        <v>122.5221134900019</v>
+        <v>56.99830821316132</v>
       </c>
       <c r="D4" t="n">
-        <v>110.410292062709</v>
+        <v>85.16563159570654</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.72870314292517</v>
+        <v>23.66011967234813</v>
       </c>
       <c r="C5" t="n">
-        <v>142.3288734231814</v>
+        <v>140.5617275555371</v>
       </c>
       <c r="D5" t="n">
-        <v>76.94447632034378</v>
+        <v>90.02626447943253</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.87302005544945</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>141.9273386121444</v>
+        <v>236.8004915074434</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>58.44540432922113</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>143.3685442419787</v>
+        <v>212.4178055247696</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>108.9003640935774</v>
+        <v>101.9741340401162</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>55.57968278052466</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.518002934943821</v>
+        <v>0.9601492547533805</v>
       </c>
       <c r="C2" t="n">
-        <v>4.905793278121311</v>
+        <v>10.81689620539136</v>
       </c>
       <c r="D2" t="n">
-        <v>18.65713337150638</v>
+        <v>12.5879690638526</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15604113171301</v>
+        <v>2.395464398362217</v>
       </c>
       <c r="C3" t="n">
-        <v>26.76735115628928</v>
+        <v>11.5895316486336</v>
       </c>
       <c r="D3" t="n">
-        <v>74.33302742704726</v>
+        <v>38.59250225394211</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.49763257952867</v>
+        <v>9.252972112526187</v>
       </c>
       <c r="C4" t="n">
-        <v>113.345717698407</v>
+        <v>46.60945400682157</v>
       </c>
       <c r="D4" t="n">
-        <v>122.0881810047248</v>
+        <v>86.27598824920969</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.00559705325178</v>
+        <v>21.54936210821749</v>
       </c>
       <c r="C5" t="n">
-        <v>184.6176557836127</v>
+        <v>122.7675504160637</v>
       </c>
       <c r="D5" t="n">
-        <v>95.37678946757764</v>
+        <v>99.30378028456489</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>25.60005313593983</v>
       </c>
       <c r="C6" t="n">
-        <v>180.931193154166</v>
+        <v>231.5275245879338</v>
       </c>
       <c r="D6" t="n">
-        <v>50.83784136901259</v>
+        <v>71.32593420893927</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>14.85187926984575</v>
       </c>
       <c r="C7" t="n">
-        <v>173.910715321097</v>
+        <v>277.4546639403038</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>47.13076203777662</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>146.368765226157</v>
+        <v>184.6716519073462</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>43.0594543082651</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>89.30467991681108</v>
+        <v>84.42343033129593</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>43.4874963073167</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.686061718819273</v>
+        <v>0.6293002784222055</v>
       </c>
       <c r="C2" t="n">
-        <v>2.324778563656447</v>
+        <v>5.451645001682538</v>
       </c>
       <c r="D2" t="n">
-        <v>13.01797455831271</v>
+        <v>9.062513057902306</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7745421853885</v>
+        <v>3.671736413883071</v>
       </c>
       <c r="C3" t="n">
-        <v>25.20146356801562</v>
+        <v>25.01984024272996</v>
       </c>
       <c r="D3" t="n">
-        <v>74.63736921536376</v>
+        <v>42.98582323044659</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.95632974159018</v>
+        <v>14.85580626066273</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6745621216007</v>
+        <v>65.56209343730625</v>
       </c>
       <c r="D4" t="n">
-        <v>130.8561697513531</v>
+        <v>91.38107631129311</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.52730599483434</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C5" t="n">
-        <v>218.7824758914017</v>
+        <v>189.3791321492097</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7273144557228</v>
+        <v>94.81228453763572</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>9.217629195173304</v>
       </c>
       <c r="C6" t="n">
-        <v>219.0092596110827</v>
+        <v>244.0055379089108</v>
       </c>
       <c r="D6" t="n">
-        <v>49.99255659565609</v>
+        <v>62.71207985187777</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>185.1693979933994</v>
+        <v>129.8341703912322</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>110.2355409713531</v>
+        <v>62.16917337142927</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.676244241776805</v>
+        <v>0.2925608158655495</v>
       </c>
       <c r="C2" t="n">
-        <v>4.966661635784614</v>
+        <v>3.034582153826891</v>
       </c>
       <c r="D2" t="n">
-        <v>15.99659709299753</v>
+        <v>6.538439710283757</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.64138435050943</v>
+        <v>2.891246989006857</v>
       </c>
       <c r="C3" t="n">
-        <v>16.98423528346982</v>
+        <v>22.96798754085413</v>
       </c>
       <c r="D3" t="n">
-        <v>69.0364985626357</v>
+        <v>40.19275101186442</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.37375244234432</v>
+        <v>10.33780332571891</v>
       </c>
       <c r="C4" t="n">
-        <v>87.15661593991908</v>
+        <v>62.03958267446869</v>
       </c>
       <c r="D4" t="n">
-        <v>136.5738683808866</v>
+        <v>88.54775243683682</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.67581194008286</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="C5" t="n">
-        <v>211.9838730394926</v>
+        <v>139.3836303104409</v>
       </c>
       <c r="D5" t="n">
-        <v>119.3805208364122</v>
+        <v>96.50579932746149</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.71580155404972</v>
+        <v>9.418887474543901</v>
       </c>
       <c r="C6" t="n">
-        <v>276.8911407580662</v>
+        <v>228.1061338386337</v>
       </c>
       <c r="D6" t="n">
-        <v>64.80516595733197</v>
+        <v>64.84541761320608</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>242.001790844543</v>
+        <v>169.658766014004</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>166.9805582768187</v>
+        <v>72.76713983877357</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>71.55468142402876</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>19.50241814486289</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.964477156197868</v>
+        <v>0.1678788574262046</v>
       </c>
       <c r="C2" t="n">
-        <v>2.957024085191393</v>
+        <v>4.112541133089889</v>
       </c>
       <c r="D2" t="n">
-        <v>11.84282255632927</v>
+        <v>14.44838096340031</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.87914722138641</v>
+        <v>1.840776945462769</v>
       </c>
       <c r="C3" t="n">
-        <v>18.19669369821463</v>
+        <v>16.22338081267854</v>
       </c>
       <c r="D3" t="n">
-        <v>67.25462647942776</v>
+        <v>36.35902622678062</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.23412328416303</v>
+        <v>7.798022014832415</v>
       </c>
       <c r="C4" t="n">
-        <v>70.51402885752717</v>
+        <v>59.41046232249573</v>
       </c>
       <c r="D4" t="n">
-        <v>139.0881242514626</v>
+        <v>88.91787132133787</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.24093876483053</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C5" t="n">
-        <v>199.932919969863</v>
+        <v>126.6209101552324</v>
       </c>
       <c r="D5" t="n">
-        <v>132.0205225285899</v>
+        <v>107.0104997629024</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.9548082145382</v>
+        <v>15.37613254391355</v>
       </c>
       <c r="C6" t="n">
-        <v>309.6559886395993</v>
+        <v>225.7312861420607</v>
       </c>
       <c r="D6" t="n">
-        <v>77.24292762243481</v>
+        <v>80.06054353362315</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>298.4748640359323</v>
+        <v>259.3689077326691</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>45.6934833987593</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>209.288975591335</v>
+        <v>153.6287894990621</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>80.87343063273947</v>
+        <v>62.34686970589792</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>18.30272245027328</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.386628669023996</v>
+        <v>0.1845685683984004</v>
       </c>
       <c r="C2" t="n">
-        <v>9.557313900842699</v>
+        <v>5.038329218194631</v>
       </c>
       <c r="D2" t="n">
-        <v>21.70545999319273</v>
+        <v>12.96986892080461</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.405143006684444</v>
+        <v>1.153553552490002</v>
       </c>
       <c r="C3" t="n">
-        <v>14.98637870532756</v>
+        <v>16.21847207415731</v>
       </c>
       <c r="D3" t="n">
-        <v>61.98264130762237</v>
+        <v>39.25027321578748</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.18008610270045</v>
+        <v>5.590071427981338</v>
       </c>
       <c r="C4" t="n">
-        <v>59.24454696047802</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="D4" t="n">
-        <v>140.0070401026376</v>
+        <v>87.23319226085034</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.99550183876883</v>
+        <v>14.13716694115407</v>
       </c>
       <c r="C5" t="n">
-        <v>169.817809142092</v>
+        <v>117.5642875835556</v>
       </c>
       <c r="D5" t="n">
-        <v>146.2067768549562</v>
+        <v>114.7908503190583</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.81017250684443</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="C6" t="n">
-        <v>314.0434191298783</v>
+        <v>214.2595642179367</v>
       </c>
       <c r="D6" t="n">
-        <v>93.62535156320133</v>
+        <v>93.7461065308237</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.42806736124739</v>
+        <v>12.81573453123786</v>
       </c>
       <c r="C7" t="n">
-        <v>361.6552375427357</v>
+        <v>296.6782657371606</v>
       </c>
       <c r="D7" t="n">
-        <v>51.50248456478767</v>
+        <v>57.43125895073415</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>280.0533501134451</v>
+        <v>251.2635986864074</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>145.4390501502352</v>
+        <v>126.2468642799143</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>51.10487674456772</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.403138453546944</v>
+        <v>2.175552912610932</v>
       </c>
       <c r="C2" t="n">
-        <v>11.72697632722815</v>
+        <v>8.09156457840221</v>
       </c>
       <c r="D2" t="n">
-        <v>13.99383177633403</v>
+        <v>5.039310965898878</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.726894211770139</v>
+        <v>0.7048948516492098</v>
       </c>
       <c r="C2" t="n">
-        <v>5.504659377711866</v>
+        <v>17.92376783643402</v>
       </c>
       <c r="D2" t="n">
-        <v>16.14876798715579</v>
+        <v>16.78297700409922</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.47310458245573</v>
+        <v>0.8786641953008953</v>
       </c>
       <c r="C3" t="n">
-        <v>23.65030219530566</v>
+        <v>18.05924901962008</v>
       </c>
       <c r="D3" t="n">
-        <v>69.19848693383643</v>
+        <v>40.0896675029185</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.41578766717769</v>
+        <v>3.918155087649021</v>
       </c>
       <c r="C4" t="n">
-        <v>88.58604059730244</v>
+        <v>43.98033365484861</v>
       </c>
       <c r="D4" t="n">
-        <v>143.2360083019054</v>
+        <v>86.16112376781281</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.65507206510666</v>
+        <v>11.60916660271853</v>
       </c>
       <c r="C5" t="n">
-        <v>261.2185204074701</v>
+        <v>103.6725575684632</v>
       </c>
       <c r="D5" t="n">
-        <v>133.2231634662922</v>
+        <v>119.9450257663541</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.02645043475243</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>296.6547037922588</v>
+        <v>202.4658290468197</v>
       </c>
       <c r="D6" t="n">
-        <v>75.35109979635121</v>
+        <v>106.9889013134089</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>196.9071735453743</v>
+        <v>303.3855660525748</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>68.33062196328224</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>107.1479444414969</v>
+        <v>321.0265905501857</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>211.6687320264292</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>93.95325529641975</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>40.33706792438868</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.66999390265283</v>
+        <v>3.0012027318825</v>
       </c>
       <c r="C2" t="n">
-        <v>5.276893910326605</v>
+        <v>5.473243451175968</v>
       </c>
       <c r="D2" t="n">
-        <v>13.91431021229004</v>
+        <v>16.47078123414874</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.360964359993337</v>
+        <v>3.607922813107028</v>
       </c>
       <c r="C3" t="n">
-        <v>29.55060589782899</v>
+        <v>15.9730351480956</v>
       </c>
       <c r="D3" t="n">
-        <v>14.89311267342411</v>
+        <v>6.508987279156353</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39683224642141</v>
+        <v>11.67892563992592</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13635705479443</v>
+        <v>59.95181828495307</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576097911343695</v>
+        <v>0.7785950426617282</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.546473618366979</v>
+        <v>1.522690689286803</v>
       </c>
       <c r="C2" t="n">
-        <v>6.566910393706914</v>
+        <v>4.39528447191297</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51495988083985</v>
+        <v>20.76003695400305</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5143790437631</v>
+        <v>7.893251542144355</v>
       </c>
       <c r="C3" t="n">
-        <v>23.93500902953724</v>
+        <v>19.59568417676634</v>
       </c>
       <c r="D3" t="n">
-        <v>22.98271375641783</v>
+        <v>19.36497346626834</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.00146477378976</v>
+        <v>4.683918296961533</v>
       </c>
       <c r="C4" t="n">
-        <v>45.57567367424968</v>
+        <v>26.52093248252334</v>
       </c>
       <c r="D4" t="n">
-        <v>22.8707945181337</v>
+        <v>17.56150293356694</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43777718188133</v>
+        <v>13.63243677307979</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12654638312742</v>
+        <v>73.77554018372591</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25005835408028</v>
+        <v>1.603816090950563</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.292200962967055</v>
+        <v>2.949170103557418</v>
       </c>
       <c r="C2" t="n">
-        <v>6.326382206166446</v>
+        <v>7.591854996940584</v>
       </c>
       <c r="D2" t="n">
-        <v>19.22262004915255</v>
+        <v>17.8668264695877</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.51790512395258</v>
+        <v>6.454991155422778</v>
       </c>
       <c r="C3" t="n">
-        <v>25.14746744428205</v>
+        <v>18.03470532701391</v>
       </c>
       <c r="D3" t="n">
-        <v>30.86123908299849</v>
+        <v>32.12278488295564</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.96838845148163</v>
+        <v>11.03975293425538</v>
       </c>
       <c r="C4" t="n">
-        <v>53.46303473016855</v>
+        <v>40.73860273542564</v>
       </c>
       <c r="D4" t="n">
-        <v>29.25215459573796</v>
+        <v>23.45787964527329</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.989282890711298</v>
+        <v>5.031456984264904</v>
       </c>
       <c r="C5" t="n">
-        <v>50.33911353525522</v>
+        <v>31.83316931020283</v>
       </c>
       <c r="D5" t="n">
-        <v>30.87596529856219</v>
+        <v>26.38446955163304</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72802563378873</v>
+        <v>14.84784407166874</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0409563661113</v>
+        <v>87.4373039776048</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182006408447183</v>
+        <v>2.474640678611456</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.82921695719006</v>
+        <v>1.9546596791554</v>
       </c>
       <c r="C2" t="n">
-        <v>5.830599615521806</v>
+        <v>8.2486442110817</v>
       </c>
       <c r="D2" t="n">
-        <v>24.09208866221672</v>
+        <v>17.08535529700724</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4968875115359</v>
+        <v>8.644288535893166</v>
       </c>
       <c r="C3" t="n">
-        <v>24.78912953223196</v>
+        <v>25.44690049407733</v>
       </c>
       <c r="D3" t="n">
-        <v>38.60231973098459</v>
+        <v>38.96065764303467</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.05245890114836</v>
+        <v>11.94590606527519</v>
       </c>
       <c r="C4" t="n">
-        <v>58.74680087442488</v>
+        <v>43.03589236336318</v>
       </c>
       <c r="D4" t="n">
-        <v>37.66278717802039</v>
+        <v>34.05093737409637</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.92380889416302</v>
+        <v>11.31464229144449</v>
       </c>
       <c r="C5" t="n">
-        <v>76.47814616082654</v>
+        <v>57.50587177625693</v>
       </c>
       <c r="D5" t="n">
-        <v>34.01755795215198</v>
+        <v>29.15790681613028</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>5.836490101747288</v>
       </c>
       <c r="C6" t="n">
-        <v>47.0944373727195</v>
+        <v>33.12711278440013</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04905996138355</v>
+        <v>16.09916177477642</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7486292718832</v>
+        <v>101.6789164722721</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016353320461183</v>
+        <v>3.389297215742404</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.608724634362028</v>
+        <v>1.993929587325272</v>
       </c>
       <c r="C2" t="n">
-        <v>8.955502558139404</v>
+        <v>6.397068040872216</v>
       </c>
       <c r="D2" t="n">
-        <v>26.06343805234432</v>
+        <v>14.10771451002667</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.31388152791849</v>
+        <v>7.579092276785376</v>
       </c>
       <c r="C3" t="n">
-        <v>22.11386703815941</v>
+        <v>29.3935262651495</v>
       </c>
       <c r="D3" t="n">
-        <v>45.46473618366979</v>
+        <v>43.58959806855839</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.22440361811179</v>
+        <v>14.67712817848981</v>
       </c>
       <c r="C4" t="n">
-        <v>50.14472748981433</v>
+        <v>55.00732386894879</v>
       </c>
       <c r="D4" t="n">
-        <v>41.82343394861837</v>
+        <v>45.92026711844031</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.78221624057323</v>
+        <v>14.75075925630833</v>
       </c>
       <c r="C5" t="n">
-        <v>69.60591223109887</v>
+        <v>69.87589284976674</v>
       </c>
       <c r="D5" t="n">
-        <v>31.80862561759666</v>
+        <v>34.87658719336795</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>10.78744377426395</v>
       </c>
       <c r="C6" t="n">
-        <v>57.47936458824226</v>
+        <v>64.44290105446488</v>
       </c>
       <c r="D6" t="n">
-        <v>31.47679489356124</v>
+        <v>35.34095385747668</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>28.7455727803466</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052106139284721</v>
+        <v>17.38041977769491</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11349505579426</v>
+        <v>115.5797915216712</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407566337052951</v>
+        <v>4.345104944423729</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.268639018065131</v>
+        <v>2.870630287217673</v>
       </c>
       <c r="C2" t="n">
-        <v>9.000662952534757</v>
+        <v>6.508005531452105</v>
       </c>
       <c r="D2" t="n">
-        <v>21.56703356689393</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.51928778228433</v>
+        <v>7.215845626214056</v>
       </c>
       <c r="C3" t="n">
-        <v>30.41945261608742</v>
+        <v>26.76735115628928</v>
       </c>
       <c r="D3" t="n">
-        <v>56.37195317785186</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.34676222824415</v>
+        <v>14.54950097693773</v>
       </c>
       <c r="C4" t="n">
-        <v>53.5396110510998</v>
+        <v>65.16644911249479</v>
       </c>
       <c r="D4" t="n">
-        <v>55.54335811546755</v>
+        <v>56.81963013098839</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.04714925199963</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="C5" t="n">
-        <v>83.86579763528378</v>
+        <v>86.68832228499336</v>
       </c>
       <c r="D5" t="n">
-        <v>40.61981126321179</v>
+        <v>43.02509313861647</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.00507296943726</v>
+        <v>15.25537757629119</v>
       </c>
       <c r="C6" t="n">
-        <v>88.87565617005527</v>
+        <v>88.31213298781759</v>
       </c>
       <c r="D6" t="n">
-        <v>34.97868895460962</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.82140403328509</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>60.42558944868693</v>
+        <v>63.18037350680348</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>35.29873870619407</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.272688717195861</v>
+        <v>18.68588604123814</v>
       </c>
       <c r="C21" t="n">
-        <v>75.45414544090706</v>
+        <v>129.0215940942633</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454516537896895</v>
+        <v>5.338824583210897</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.735550014659113</v>
+        <v>2.50542014123786</v>
       </c>
       <c r="C2" t="n">
-        <v>8.02382398680918</v>
+        <v>3.904410619789565</v>
       </c>
       <c r="D2" t="n">
-        <v>22.78047372934299</v>
+        <v>10.98673855822605</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.97794388661684</v>
+        <v>9.866564427680444</v>
       </c>
       <c r="C3" t="n">
-        <v>33.50214040742241</v>
+        <v>40.14366362665208</v>
       </c>
       <c r="D3" t="n">
-        <v>60.54438092090079</v>
+        <v>49.96114066912018</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.45185029032756</v>
+        <v>8.870090507869932</v>
       </c>
       <c r="C4" t="n">
-        <v>66.13641584429062</v>
+        <v>85.17839431586177</v>
       </c>
       <c r="D4" t="n">
-        <v>71.3308429474605</v>
+        <v>54.08840801777377</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.011266555299</v>
+        <v>8.590292412159592</v>
       </c>
       <c r="C5" t="n">
-        <v>92.55426481786806</v>
+        <v>52.76893910326607</v>
       </c>
       <c r="D5" t="n">
-        <v>51.05088062083415</v>
+        <v>35.53926689373454</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.18245050873644</v>
+        <v>6.118251692866123</v>
       </c>
       <c r="C6" t="n">
-        <v>113.5499212208904</v>
+        <v>41.57996051796516</v>
       </c>
       <c r="D6" t="n">
-        <v>40.25165587411923</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>97.07619474362885</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>57.49605429921444</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.480503572793667</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.15566519392875</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.545440626194459</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
